--- a/Luban/Config/Datas/#PasserbyConfig.xlsx
+++ b/Luban/Config/Datas/#PasserbyConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F4BD41C-221E-4426-A75F-6C7E6B6B29EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D6C5BDC-96A0-4625-9312-E4CFDF589079}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6285" yWindow="4860" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6330" yWindow="3720" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="47">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -71,10 +71,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Kc</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>TriggerDate</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -148,6 +144,71 @@
   </si>
   <si>
     <t>TimePeriod#sep=,</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Kc1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Kc2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Kc3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Kc4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Passerby1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Passerby2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Passerby3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Passerby4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,3,4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3,4,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3,4,2</t>
+  </si>
+  <si>
+    <t>3,4,3</t>
+  </si>
+  <si>
+    <t>3,4,4</t>
+  </si>
+  <si>
+    <t>1,-3,-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,-2,0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,-5,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,5,3</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -198,7 +259,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -208,6 +269,9 @@
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -489,22 +553,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="9" style="3"/>
     <col min="3" max="3" width="48.125" style="3" customWidth="1"/>
     <col min="4" max="4" width="36.125" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9" style="3"/>
-    <col min="6" max="6" width="19.5" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.5" style="3" customWidth="1"/>
-    <col min="8" max="8" width="12.875" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17" style="3" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.25" style="3" customWidth="1"/>
-    <col min="11" max="16384" width="9" style="3"/>
+    <col min="5" max="6" width="36.125" style="3" customWidth="1"/>
+    <col min="7" max="7" width="9" style="3"/>
+    <col min="8" max="8" width="19.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="22.5" style="3" customWidth="1"/>
+    <col min="10" max="10" width="12.875" style="3" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17" style="3" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.25" style="3" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -514,32 +579,34 @@
       <c r="C1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="I1" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="L1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -550,31 +617,31 @@
         <v>6</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>13</v>
-      </c>
       <c r="H2" s="3" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>4</v>
       </c>
       <c r="K2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M2" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -585,124 +652,222 @@
         <v>10</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E3" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>14</v>
-      </c>
       <c r="H3" s="3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>19</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+        <v>20</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B4" s="2">
         <v>1</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
+        <v>30</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="F4" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+        <v>39</v>
+      </c>
+      <c r="G4" s="2">
+        <v>25</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B5" s="2">
+        <v>2</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="G5" s="2">
+        <v>25</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B6" s="2">
+        <v>3</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G6" s="2">
+        <v>25</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="B7" s="2">
+        <v>4</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G7" s="2">
+        <v>25</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="D1:F1"/>
+  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
